--- a/Outputs/Canada_LNG_Emissions_Results.xlsx
+++ b/Outputs/Canada_LNG_Emissions_Results.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Territorial" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Chain" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrification CAN" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +467,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-20 10:03 UTC</t>
+          <t>2026-08-21 15:47 UTC</t>
         </is>
       </c>
     </row>
@@ -537,7 +538,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>259.2219377314999</v>
+        <v>271.9961689814999</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +548,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95.10000000000001</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="11">
@@ -557,7 +558,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47.97030229399999</v>
+        <v>50.27326229399998</v>
       </c>
     </row>
     <row r="12">
@@ -567,7 +568,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.7600961875</v>
+        <v>15.1919011875</v>
       </c>
     </row>
     <row r="13">
@@ -577,7 +578,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>196.4915392499999</v>
+        <v>206.5310054999999</v>
       </c>
     </row>
     <row r="14">
@@ -607,10 +608,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>slide_tables</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Outputs/SLIDE_TABLES.xlsx — send this file to the PPT chat (one table per sheet, 1-decimal, project names).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>findings</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>tilbury_marine_jetty: chain=none — no lifecycle applies; excluded (not zeroed).</t>
         </is>
@@ -824,10 +837,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="E4" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="F4" t="n">
         <v>3.15</v>
@@ -839,25 +852,25 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>34.44059618749998</v>
+        <v>36.63560493749998</v>
       </c>
       <c r="J4" t="n">
-        <v>163.9645036124999</v>
+        <v>174.4357748624999</v>
       </c>
       <c r="K4" t="n">
-        <v>34.44059618749998</v>
+        <v>36.63560493749998</v>
       </c>
       <c r="L4" t="n">
-        <v>12.2666096625</v>
+        <v>12.6984146625</v>
       </c>
       <c r="M4" t="n">
-        <v>151.6978939499999</v>
+        <v>161.7373601999999</v>
       </c>
       <c r="N4" t="n">
-        <v>198.4050997999999</v>
+        <v>211.0713797999999</v>
       </c>
       <c r="O4" t="n">
-        <v>7789.928215999997</v>
+        <v>8296.579415999997</v>
       </c>
     </row>
     <row r="5">
@@ -977,10 +990,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="E7" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="F7" t="n">
         <v>3.15</v>
@@ -992,25 +1005,25 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>36.13439599999998</v>
+        <v>38.43735599999998</v>
       </c>
       <c r="J7" t="n">
-        <v>163.9645036124999</v>
+        <v>174.4357748624999</v>
       </c>
       <c r="K7" t="n">
-        <v>36.13439599999998</v>
+        <v>38.43735599999998</v>
       </c>
       <c r="L7" t="n">
-        <v>12.2666096625</v>
+        <v>12.6984146625</v>
       </c>
       <c r="M7" t="n">
-        <v>151.6978939499999</v>
+        <v>161.7373601999999</v>
       </c>
       <c r="N7" t="n">
-        <v>200.0988996124999</v>
+        <v>212.8731308624999</v>
       </c>
       <c r="O7" t="n">
-        <v>7856.400399499997</v>
+        <v>8367.369649499997</v>
       </c>
     </row>
     <row r="8">
@@ -1130,10 +1143,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="E10" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="F10" t="n">
         <v>3.15</v>
@@ -1145,25 +1158,25 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>36.69899593749998</v>
+        <v>39.03793968749998</v>
       </c>
       <c r="J10" t="n">
-        <v>163.9645036124999</v>
+        <v>174.4357748624999</v>
       </c>
       <c r="K10" t="n">
-        <v>36.69899593749998</v>
+        <v>39.03793968749998</v>
       </c>
       <c r="L10" t="n">
-        <v>12.2666096625</v>
+        <v>12.6984146625</v>
       </c>
       <c r="M10" t="n">
-        <v>151.6978939499999</v>
+        <v>161.7373601999999</v>
       </c>
       <c r="N10" t="n">
-        <v>200.6634995499999</v>
+        <v>213.4737145499999</v>
       </c>
       <c r="O10" t="n">
-        <v>7878.557793999996</v>
+        <v>8390.966393999995</v>
       </c>
     </row>
     <row r="11">
@@ -1283,10 +1296,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="E13" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="F13" t="n">
         <v>3.15</v>
@@ -1298,25 +1311,25 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>40.65119549999999</v>
+        <v>43.24202549999998</v>
       </c>
       <c r="J13" t="n">
-        <v>163.9645036124999</v>
+        <v>174.4357748624999</v>
       </c>
       <c r="K13" t="n">
-        <v>40.65119549999999</v>
+        <v>43.24202549999998</v>
       </c>
       <c r="L13" t="n">
-        <v>12.2666096625</v>
+        <v>12.6984146625</v>
       </c>
       <c r="M13" t="n">
-        <v>151.6978939499999</v>
+        <v>161.7373601999999</v>
       </c>
       <c r="N13" t="n">
-        <v>204.6156991124999</v>
+        <v>217.6778003624999</v>
       </c>
       <c r="O13" t="n">
-        <v>8033.659555499996</v>
+        <v>8556.143605499996</v>
       </c>
     </row>
     <row r="14">
@@ -1436,10 +1449,10 @@
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="E16" t="n">
-        <v>75.7</v>
+        <v>80.7</v>
       </c>
       <c r="F16" t="n">
         <v>3.15</v>
@@ -1451,25 +1464,25 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>53.07239412499999</v>
+        <v>56.45486662499999</v>
       </c>
       <c r="J16" t="n">
-        <v>163.9645036124999</v>
+        <v>174.4357748624999</v>
       </c>
       <c r="K16" t="n">
-        <v>53.07239412499999</v>
+        <v>56.45486662499999</v>
       </c>
       <c r="L16" t="n">
-        <v>12.2666096625</v>
+        <v>12.6984146625</v>
       </c>
       <c r="M16" t="n">
-        <v>151.6978939499999</v>
+        <v>161.7373601999999</v>
       </c>
       <c r="N16" t="n">
-        <v>217.0368977374999</v>
+        <v>230.8906414874999</v>
       </c>
       <c r="O16" t="n">
-        <v>8521.122234499997</v>
+        <v>9075.271984499996</v>
       </c>
     </row>
   </sheetData>
@@ -3860,7 +3873,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Marinvest Energy LNG Export Project (Baie-Comeau)</t>
+          <t>Kino Aski LNG (formerly Marinvest Energy, Baie-Comeau)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -3903,7 +3916,7 @@
         <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
         <v>40</v>
@@ -3932,7 +3945,7 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>7196749.999999996</v>
+        <v>10795124.99999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.22</v>
@@ -3953,22 +3966,22 @@
         <v>2.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1583284.999999999</v>
+        <v>2374927.499999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>719674.9999999997</v>
+        <v>1079512.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>2087057.499999999</v>
+        <v>3130586.249999998</v>
       </c>
       <c r="AE15" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AF15" t="n">
-        <v>287869.9999999999</v>
+        <v>431804.9999999998</v>
       </c>
       <c r="AG15" t="n">
-        <v>19791062.49999999</v>
+        <v>29686593.74999999</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -4001,25 +4014,25 @@
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>4390017.499999998</v>
+        <v>6585026.249999996</v>
       </c>
       <c r="AO15" t="n">
-        <v>20942542.49999999</v>
+        <v>31413813.74999999</v>
       </c>
       <c r="AP15" t="n">
-        <v>25332559.99999999</v>
+        <v>37998839.99999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1013302399.999999</v>
+        <v>1519953600</v>
       </c>
       <c r="AR15" t="n">
-        <v>4390017.499999998</v>
+        <v>6585026.249999996</v>
       </c>
       <c r="AS15" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>20078932.49999999</v>
+        <v>30118398.74999999</v>
       </c>
       <c r="AU15" t="b">
         <v>0</v>
@@ -7001,7 +7014,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marinvest Energy LNG Export Project (Baie-Comeau)</t>
+          <t>Kino Aski LNG (formerly Marinvest Energy, Baie-Comeau)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -7044,7 +7057,7 @@
         <v>6</v>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M34" t="n">
         <v>40</v>
@@ -7073,7 +7086,7 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>7196749.999999996</v>
+        <v>10795124.99999999</v>
       </c>
       <c r="V34" t="n">
         <v>0.25</v>
@@ -7094,22 +7107,22 @@
         <v>2.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>1799187.499999999</v>
+        <v>2698781.249999999</v>
       </c>
       <c r="AC34" t="n">
-        <v>719674.9999999997</v>
+        <v>1079512.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>2087057.499999999</v>
+        <v>3130586.249999998</v>
       </c>
       <c r="AE34" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AF34" t="n">
-        <v>287869.9999999999</v>
+        <v>431804.9999999998</v>
       </c>
       <c r="AG34" t="n">
-        <v>19791062.49999999</v>
+        <v>29686593.74999999</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -7142,25 +7155,25 @@
         </is>
       </c>
       <c r="AN34" t="n">
-        <v>4605919.999999997</v>
+        <v>6908879.999999996</v>
       </c>
       <c r="AO34" t="n">
-        <v>20942542.49999999</v>
+        <v>31413813.74999999</v>
       </c>
       <c r="AP34" t="n">
-        <v>25548462.49999999</v>
+        <v>38322693.74999999</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1021938499.999999</v>
+        <v>1532907750</v>
       </c>
       <c r="AR34" t="n">
-        <v>4605919.999999997</v>
+        <v>6908879.999999996</v>
       </c>
       <c r="AS34" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AT34" t="n">
-        <v>20078932.49999999</v>
+        <v>30118398.74999999</v>
       </c>
       <c r="AU34" t="b">
         <v>0</v>
@@ -10142,7 +10155,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marinvest Energy LNG Export Project (Baie-Comeau)</t>
+          <t>Kino Aski LNG (formerly Marinvest Energy, Baie-Comeau)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -10185,7 +10198,7 @@
         <v>6</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M53" t="n">
         <v>40</v>
@@ -10214,7 +10227,7 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>7196749.999999996</v>
+        <v>10795124.99999999</v>
       </c>
       <c r="V53" t="n">
         <v>0.26</v>
@@ -10235,22 +10248,22 @@
         <v>2.75</v>
       </c>
       <c r="AB53" t="n">
-        <v>1871154.999999999</v>
+        <v>2806732.499999999</v>
       </c>
       <c r="AC53" t="n">
-        <v>719674.9999999997</v>
+        <v>1079512.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>2087057.499999999</v>
+        <v>3130586.249999998</v>
       </c>
       <c r="AE53" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AF53" t="n">
-        <v>287869.9999999999</v>
+        <v>431804.9999999998</v>
       </c>
       <c r="AG53" t="n">
-        <v>19791062.49999999</v>
+        <v>29686593.74999999</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -10283,25 +10296,25 @@
         </is>
       </c>
       <c r="AN53" t="n">
-        <v>4677887.499999997</v>
+        <v>7016831.249999996</v>
       </c>
       <c r="AO53" t="n">
-        <v>20942542.49999999</v>
+        <v>31413813.74999999</v>
       </c>
       <c r="AP53" t="n">
-        <v>25620429.99999999</v>
+        <v>38430644.99999999</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1024817199.999999</v>
+        <v>1537225800</v>
       </c>
       <c r="AR53" t="n">
-        <v>4677887.499999997</v>
+        <v>7016831.249999996</v>
       </c>
       <c r="AS53" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AT53" t="n">
-        <v>20078932.49999999</v>
+        <v>30118398.74999999</v>
       </c>
       <c r="AU53" t="b">
         <v>0</v>
@@ -13283,7 +13296,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Marinvest Energy LNG Export Project (Baie-Comeau)</t>
+          <t>Kino Aski LNG (formerly Marinvest Energy, Baie-Comeau)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -13326,7 +13339,7 @@
         <v>6</v>
       </c>
       <c r="L72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M72" t="n">
         <v>40</v>
@@ -13355,7 +13368,7 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>7196749.999999996</v>
+        <v>10795124.99999999</v>
       </c>
       <c r="V72" t="n">
         <v>0.33</v>
@@ -13376,22 +13389,22 @@
         <v>2.75</v>
       </c>
       <c r="AB72" t="n">
-        <v>2374927.499999999</v>
+        <v>3562391.249999998</v>
       </c>
       <c r="AC72" t="n">
-        <v>719674.9999999997</v>
+        <v>1079512.5</v>
       </c>
       <c r="AD72" t="n">
-        <v>2087057.499999999</v>
+        <v>3130586.249999998</v>
       </c>
       <c r="AE72" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AF72" t="n">
-        <v>287869.9999999999</v>
+        <v>431804.9999999998</v>
       </c>
       <c r="AG72" t="n">
-        <v>19791062.49999999</v>
+        <v>29686593.74999999</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -13424,25 +13437,25 @@
         </is>
       </c>
       <c r="AN72" t="n">
-        <v>5181659.999999997</v>
+        <v>7772489.999999996</v>
       </c>
       <c r="AO72" t="n">
-        <v>20942542.49999999</v>
+        <v>31413813.74999999</v>
       </c>
       <c r="AP72" t="n">
-        <v>26124202.49999999</v>
+        <v>39186303.74999999</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1044968099.999999</v>
+        <v>1567452150</v>
       </c>
       <c r="AR72" t="n">
-        <v>5181659.999999997</v>
+        <v>7772489.999999996</v>
       </c>
       <c r="AS72" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AT72" t="n">
-        <v>20078932.49999999</v>
+        <v>30118398.74999999</v>
       </c>
       <c r="AU72" t="b">
         <v>0</v>
@@ -16424,7 +16437,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Marinvest Energy LNG Export Project (Baie-Comeau)</t>
+          <t>Kino Aski LNG (formerly Marinvest Energy, Baie-Comeau)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -16467,7 +16480,7 @@
         <v>6</v>
       </c>
       <c r="L91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M91" t="n">
         <v>40</v>
@@ -16496,7 +16509,7 @@
         </is>
       </c>
       <c r="U91" t="n">
-        <v>7196749.999999996</v>
+        <v>10795124.99999999</v>
       </c>
       <c r="V91" t="n">
         <v>0.55</v>
@@ -16517,22 +16530,22 @@
         <v>2.75</v>
       </c>
       <c r="AB91" t="n">
-        <v>3958212.499999998</v>
+        <v>5937318.749999997</v>
       </c>
       <c r="AC91" t="n">
-        <v>719674.9999999997</v>
+        <v>1079512.5</v>
       </c>
       <c r="AD91" t="n">
-        <v>2087057.499999999</v>
+        <v>3130586.249999998</v>
       </c>
       <c r="AE91" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AF91" t="n">
-        <v>287869.9999999999</v>
+        <v>431804.9999999998</v>
       </c>
       <c r="AG91" t="n">
-        <v>19791062.49999999</v>
+        <v>29686593.74999999</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -16565,25 +16578,25 @@
         </is>
       </c>
       <c r="AN91" t="n">
-        <v>6764944.999999997</v>
+        <v>10147417.49999999</v>
       </c>
       <c r="AO91" t="n">
-        <v>20942542.49999999</v>
+        <v>31413813.74999999</v>
       </c>
       <c r="AP91" t="n">
-        <v>27707487.49999999</v>
+        <v>41561231.24999998</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1108299500</v>
+        <v>1662449249.999999</v>
       </c>
       <c r="AR91" t="n">
-        <v>6764944.999999997</v>
+        <v>10147417.49999999</v>
       </c>
       <c r="AS91" t="n">
-        <v>863609.9999999995</v>
+        <v>1295414.999999999</v>
       </c>
       <c r="AT91" t="n">
-        <v>20078932.49999999</v>
+        <v>30118398.74999999</v>
       </c>
       <c r="AU91" t="b">
         <v>0</v>
@@ -17509,13 +17522,13 @@
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>18246306.7625</v>
+        <v>19145900.5125</v>
       </c>
       <c r="G2" t="n">
-        <v>18.24630676249999</v>
+        <v>19.1459005125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07038874457222591</v>
+        <v>0.07039033154103808</v>
       </c>
     </row>
     <row r="3">
@@ -17543,13 +17556,13 @@
         <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>7298522.704999998</v>
+        <v>7658360.204999998</v>
       </c>
       <c r="G3" t="n">
-        <v>7.298522704999998</v>
+        <v>7.658360204999998</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02815549782889036</v>
+        <v>0.02815613261641523</v>
       </c>
     </row>
     <row r="4">
@@ -17577,13 +17590,13 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>21165715.84449999</v>
+        <v>22209244.59449999</v>
       </c>
       <c r="G4" t="n">
-        <v>21.16571584449999</v>
+        <v>22.20924459449999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08165094370378204</v>
+        <v>0.08165278458760415</v>
       </c>
     </row>
     <row r="5">
@@ -17611,13 +17624,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8451248.999999996</v>
+        <v>8883053.999999996</v>
       </c>
       <c r="G5" t="n">
-        <v>8.451248999999997</v>
+        <v>8.883053999999996</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03260236797069905</v>
+        <v>0.03265874675096687</v>
       </c>
     </row>
     <row r="6">
@@ -17645,13 +17658,13 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>2835144.032</v>
+        <v>2979079.032</v>
       </c>
       <c r="G6" t="n">
-        <v>2.835144032</v>
+        <v>2.979079032</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01093713000068929</v>
+        <v>0.01095265070517455</v>
       </c>
     </row>
     <row r="7">
@@ -17679,13 +17692,13 @@
         <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>201224999.3875</v>
+        <v>211120530.6375</v>
       </c>
       <c r="G7" t="n">
-        <v>201.2249993875</v>
+        <v>211.1205306375</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7762653159237135</v>
+        <v>0.7761893537988013</v>
       </c>
     </row>
   </sheetData>
@@ -17771,22 +17784,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47.97030229399999</v>
+        <v>50.27326229399998</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1850549483342234</v>
+        <v>0.1848307734710019</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06912147304610949</v>
+        <v>0.07243985921325645</v>
       </c>
       <c r="F2" t="n">
-        <v>0.115036696148681</v>
+        <v>0.120559382</v>
       </c>
       <c r="G2" t="n">
-        <v>0.105429235810989</v>
+        <v>0.1104906863604395</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2398515114699999</v>
+        <v>0.2513663114699999</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -17804,10 +17817,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.7600961875</v>
+        <v>15.1919011875</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05693999634702367</v>
+        <v>0.0558533645690182</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -17829,10 +17842,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>196.4915392499999</v>
+        <v>206.5310054999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.758005055318753</v>
+        <v>0.7593158619599798</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -17928,29 +17941,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>200.0988996124999</v>
+        <v>212.8731308624999</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.05206685302593658</v>
+        <v>0.05538523919308354</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08665322781774576</v>
+        <v>0.0921759136690647</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0794162549450549</v>
+        <v>0.08447770549450545</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1806719799999999</v>
+        <v>0.1921867799999999</v>
       </c>
       <c r="I7" t="n">
-        <v>36.13439599999998</v>
+        <v>38.43735599999998</v>
       </c>
       <c r="J7" t="n">
-        <v>12.2666096625</v>
+        <v>12.6984146625</v>
       </c>
       <c r="K7" t="n">
-        <v>151.6978939499999</v>
+        <v>161.7373601999999</v>
       </c>
     </row>
   </sheetData>
@@ -20409,52 +20422,52 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>95.10000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>42.96051574999998</v>
+        <v>45.15552449999998</v>
       </c>
       <c r="F2" t="n">
-        <v>204.9427882499999</v>
+        <v>215.4140594999999</v>
       </c>
       <c r="G2" t="n">
-        <v>42.96051574999998</v>
+        <v>45.15552449999998</v>
       </c>
       <c r="H2" t="n">
-        <v>8.451248999999997</v>
+        <v>8.883053999999996</v>
       </c>
       <c r="I2" t="n">
-        <v>196.4915392499999</v>
+        <v>206.5310054999999</v>
       </c>
       <c r="J2" t="n">
-        <v>247.9033039999999</v>
+        <v>260.569584</v>
       </c>
       <c r="K2" t="n">
-        <v>9851.514463999996</v>
+        <v>10358.165664</v>
       </c>
       <c r="L2" t="n">
-        <v>42960515.74999999</v>
+        <v>45155524.49999999</v>
       </c>
       <c r="M2" t="n">
-        <v>204942788.2499999</v>
+        <v>215414059.4999999</v>
       </c>
       <c r="N2" t="n">
-        <v>42960515.74999999</v>
+        <v>45155524.49999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8451248.999999996</v>
+        <v>8883053.999999996</v>
       </c>
       <c r="P2" t="n">
-        <v>196491539.2499999</v>
+        <v>206531005.4999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>247903303.9999999</v>
+        <v>260569583.9999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9851514463.999996</v>
+        <v>10358165664</v>
       </c>
     </row>
     <row r="3">
@@ -20649,52 +20662,52 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>95.10000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>45.07332799999998</v>
+        <v>47.37628799999999</v>
       </c>
       <c r="F6" t="n">
-        <v>204.9427882499999</v>
+        <v>215.4140594999999</v>
       </c>
       <c r="G6" t="n">
-        <v>45.07332799999998</v>
+        <v>47.37628799999999</v>
       </c>
       <c r="H6" t="n">
-        <v>8.451248999999997</v>
+        <v>8.883053999999996</v>
       </c>
       <c r="I6" t="n">
-        <v>196.4915392499999</v>
+        <v>206.5310054999999</v>
       </c>
       <c r="J6" t="n">
-        <v>250.01611625</v>
+        <v>262.7903474999999</v>
       </c>
       <c r="K6" t="n">
-        <v>9935.476234999996</v>
+        <v>10446.445485</v>
       </c>
       <c r="L6" t="n">
-        <v>45073327.99999999</v>
+        <v>47376287.99999999</v>
       </c>
       <c r="M6" t="n">
-        <v>204942788.2499999</v>
+        <v>215414059.4999999</v>
       </c>
       <c r="N6" t="n">
-        <v>45073327.99999999</v>
+        <v>47376287.99999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8451248.999999996</v>
+        <v>8883053.999999996</v>
       </c>
       <c r="P6" t="n">
-        <v>196491539.2499999</v>
+        <v>206531005.4999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>250016116.2499999</v>
+        <v>262790347.4999999</v>
       </c>
       <c r="R6" t="n">
-        <v>9935476234.999996</v>
+        <v>10446445485</v>
       </c>
     </row>
     <row r="7">
@@ -20889,52 +20902,52 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>95.10000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>45.77759874999999</v>
+        <v>48.11654249999999</v>
       </c>
       <c r="F10" t="n">
-        <v>204.9427882499999</v>
+        <v>215.4140594999999</v>
       </c>
       <c r="G10" t="n">
-        <v>45.77759874999999</v>
+        <v>48.11654249999999</v>
       </c>
       <c r="H10" t="n">
-        <v>8.451248999999997</v>
+        <v>8.883053999999996</v>
       </c>
       <c r="I10" t="n">
-        <v>196.4915392499999</v>
+        <v>206.5310054999999</v>
       </c>
       <c r="J10" t="n">
-        <v>250.7203869999999</v>
+        <v>263.5306019999999</v>
       </c>
       <c r="K10" t="n">
-        <v>9963.463491999995</v>
+        <v>10475.872092</v>
       </c>
       <c r="L10" t="n">
-        <v>45777598.74999999</v>
+        <v>48116542.49999999</v>
       </c>
       <c r="M10" t="n">
-        <v>204942788.2499999</v>
+        <v>215414059.4999999</v>
       </c>
       <c r="N10" t="n">
-        <v>45777598.74999999</v>
+        <v>48116542.49999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8451248.999999996</v>
+        <v>8883053.999999996</v>
       </c>
       <c r="P10" t="n">
-        <v>196491539.2499999</v>
+        <v>206531005.4999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>250720386.9999999</v>
+        <v>263530601.9999999</v>
       </c>
       <c r="R10" t="n">
-        <v>9963463491.999996</v>
+        <v>10475872092</v>
       </c>
     </row>
     <row r="11">
@@ -21129,52 +21142,52 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>95.10000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>50.70749399999998</v>
+        <v>53.29832399999998</v>
       </c>
       <c r="F14" t="n">
-        <v>204.9427882499999</v>
+        <v>215.4140594999999</v>
       </c>
       <c r="G14" t="n">
-        <v>50.70749399999998</v>
+        <v>53.29832399999998</v>
       </c>
       <c r="H14" t="n">
-        <v>8.451248999999997</v>
+        <v>8.883053999999996</v>
       </c>
       <c r="I14" t="n">
-        <v>196.4915392499999</v>
+        <v>206.5310054999999</v>
       </c>
       <c r="J14" t="n">
-        <v>255.6502822499999</v>
+        <v>268.7123834999999</v>
       </c>
       <c r="K14" t="n">
-        <v>10159.374291</v>
+        <v>10681.858341</v>
       </c>
       <c r="L14" t="n">
-        <v>50707493.99999999</v>
+        <v>53298323.99999998</v>
       </c>
       <c r="M14" t="n">
-        <v>204942788.2499999</v>
+        <v>215414059.4999999</v>
       </c>
       <c r="N14" t="n">
-        <v>50707493.99999999</v>
+        <v>53298323.99999998</v>
       </c>
       <c r="O14" t="n">
-        <v>8451248.999999996</v>
+        <v>8883053.999999996</v>
       </c>
       <c r="P14" t="n">
-        <v>196491539.2499999</v>
+        <v>206531005.4999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>255650282.2499999</v>
+        <v>268712383.4999999</v>
       </c>
       <c r="R14" t="n">
-        <v>10159374291</v>
+        <v>10681858341</v>
       </c>
     </row>
     <row r="15">
@@ -21369,52 +21382,52 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>95.10000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>66.20145049999996</v>
+        <v>69.58392299999997</v>
       </c>
       <c r="F18" t="n">
-        <v>204.9427882499999</v>
+        <v>215.4140594999999</v>
       </c>
       <c r="G18" t="n">
-        <v>66.20145049999996</v>
+        <v>69.58392299999997</v>
       </c>
       <c r="H18" t="n">
-        <v>8.451248999999997</v>
+        <v>8.883053999999996</v>
       </c>
       <c r="I18" t="n">
-        <v>196.4915392499999</v>
+        <v>206.5310054999999</v>
       </c>
       <c r="J18" t="n">
-        <v>271.1442387499999</v>
+        <v>284.9979824999999</v>
       </c>
       <c r="K18" t="n">
-        <v>10775.093945</v>
+        <v>11329.243695</v>
       </c>
       <c r="L18" t="n">
-        <v>66201450.49999997</v>
+        <v>69583922.99999997</v>
       </c>
       <c r="M18" t="n">
-        <v>204942788.2499999</v>
+        <v>215414059.4999999</v>
       </c>
       <c r="N18" t="n">
-        <v>66201450.49999997</v>
+        <v>69583922.99999997</v>
       </c>
       <c r="O18" t="n">
-        <v>8451248.999999996</v>
+        <v>8883053.999999996</v>
       </c>
       <c r="P18" t="n">
-        <v>196491539.2499999</v>
+        <v>206531005.4999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>271144238.7499999</v>
+        <v>284997982.4999999</v>
       </c>
       <c r="R18" t="n">
-        <v>10775093945</v>
+        <v>11329243695</v>
       </c>
     </row>
     <row r="19">
@@ -21595,6 +21608,276 @@
       </c>
       <c r="R21" t="n">
         <v>20925000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>canada_territorial_gas_mtco2e_yr</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>canada_territorial_claimed_electric_mtco2e_yr</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>canada_territorial_all_electric_mtco2e_yr</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta_claimed_vs_gas_mtco2e_yr</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>delta_all_electric_vs_gas_mtco2e_yr</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>liquefaction_gas_mtco2e_yr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>claimed_electric_export_mtpa</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>share_of_national_inventory_gas</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>share_of_national_inventory_all_electric</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>share_of_2030_target_low_gas</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>share_of_2030_target_low_all_electric</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>share_of_2030_target_high_gas</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>share_of_2030_target_high_all_electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>50.27326229399998</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.18811654399999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.25404994549999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-6.085145749999988</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-13.01921234849999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.20924459449999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.07243985921325645</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.05368018724135445</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.120559382</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.08933824926978413</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1104906863604395</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.08187703284725271</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>operating</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8.986261494000004</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8.986261494000004</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.933908733000004</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-2.052352761000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.501072357000002</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.01294850359365995</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.009991222958213261</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02154978775539569</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01662807849640289</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01975002526153847</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01523935985274726</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>under_construction</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.849644799999998</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.092707899999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.092707899999998</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.7569368999999995</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.7569368999999995</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.291245299999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.004106116426512966</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.003015429250720459</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.006833680575539563</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.005018484172661867</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.006262955604395599</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.004599358021978019</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>38.43735599999998</v>
+      </c>
+      <c r="C5" t="n">
+        <v>33.10914714999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>28.22743331249999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-5.328208849999996</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-10.20992268749999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17.41692693749999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05538523919308354</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.04067353503242074</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0921759136690647</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.06769168660071941</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.08447770549450545</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.06203831497252746</v>
       </c>
     </row>
   </sheetData>
